--- a/artfynd/A 37988-2024 artfynd.xlsx
+++ b/artfynd/A 37988-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125478146</v>
       </c>
       <c r="B2" t="n">
-        <v>98726</v>
+        <v>98896</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>125478152</v>
       </c>
       <c r="B3" t="n">
-        <v>98726</v>
+        <v>98896</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 37988-2024 artfynd.xlsx
+++ b/artfynd/A 37988-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125478146</v>
+        <v>125478152</v>
       </c>
       <c r="B2" t="n">
-        <v>98896</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98951</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549762</v>
+        <v>549699</v>
       </c>
       <c r="R2" t="n">
-        <v>6374784</v>
+        <v>6374791</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -782,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125478152</v>
+        <v>125478146</v>
       </c>
       <c r="B3" t="n">
-        <v>98896</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98951</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549699</v>
+        <v>549762</v>
       </c>
       <c r="R3" t="n">
-        <v>6374791</v>
+        <v>6374784</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 37988-2024 artfynd.xlsx
+++ b/artfynd/A 37988-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125478152</v>
       </c>
       <c r="B2" t="n">
-        <v>98951</v>
+        <v>98958</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125478146</v>
       </c>
       <c r="B3" t="n">
-        <v>98951</v>
+        <v>98958</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37988-2024 artfynd.xlsx
+++ b/artfynd/A 37988-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125478152</v>
       </c>
       <c r="B2" t="n">
-        <v>98958</v>
+        <v>98961</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125478146</v>
       </c>
       <c r="B3" t="n">
-        <v>98958</v>
+        <v>98961</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37988-2024 artfynd.xlsx
+++ b/artfynd/A 37988-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125478152</v>
       </c>
       <c r="B2" t="n">
-        <v>98961</v>
+        <v>98965</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125478146</v>
       </c>
       <c r="B3" t="n">
-        <v>98961</v>
+        <v>98965</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37988-2024 artfynd.xlsx
+++ b/artfynd/A 37988-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125478152</v>
       </c>
       <c r="B2" t="n">
-        <v>98965</v>
+        <v>98966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125478146</v>
       </c>
       <c r="B3" t="n">
-        <v>98965</v>
+        <v>98966</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37988-2024 artfynd.xlsx
+++ b/artfynd/A 37988-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125478152</v>
       </c>
       <c r="B2" t="n">
-        <v>98966</v>
+        <v>98968</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125478146</v>
       </c>
       <c r="B3" t="n">
-        <v>98966</v>
+        <v>98968</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
